--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260715.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260715.xlsx
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>5,900,000</t>
+          <t>790,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>790,000</t>
+          <t>5,900,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
